--- a/data/trans_orig/P70C3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023</t>
+          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>199536</t>
+          <t>197359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>236603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178925</t>
+          <t>180128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>208970</t>
+          <t>209235</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>387223</t>
+          <t>389605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>435254</t>
+          <t>437772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57474</t>
+          <t>56885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89935</t>
+          <t>89972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>56760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82053</t>
+          <t>80415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122937</t>
+          <t>121640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163191</t>
+          <t>160664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>48859</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>28005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40855</t>
+          <t>40014</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71149</t>
+          <t>70591</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20426</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29355</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43813</t>
+          <t>44795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,77 +1202,77 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10722</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6429</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17557</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>16492</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>9950</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>24392</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>3,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>10722</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6156</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16778</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>16492</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>10533</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>24339</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>21195</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163989</t>
+          <t>163820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201116</t>
+          <t>200095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132886</t>
+          <t>133033</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159944</t>
+          <t>161188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308465</t>
+          <t>307533</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>355188</t>
+          <t>354228</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,78%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55755</t>
+          <t>56648</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87719</t>
+          <t>87215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51242</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75969</t>
+          <t>75501</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113805</t>
+          <t>115341</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152763</t>
+          <t>153839</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30117</t>
+          <t>28473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27901</t>
+          <t>26495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52765</t>
+          <t>50211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29927</t>
+          <t>31196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40970</t>
+          <t>41815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19889</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>270561</t>
+          <t>266202</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>464113</t>
+          <t>460067</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>32622</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46607</t>
+          <t>46810</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>307825</t>
+          <t>309364</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>517739</t>
+          <t>516769</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105225</t>
+          <t>106235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26437</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21106</t>
+          <t>22750</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127989</t>
+          <t>127685</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30248</t>
+          <t>31027</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32832</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45359</t>
+          <t>44201</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47871</t>
+          <t>47655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36639</t>
+          <t>38771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46321</t>
+          <t>45098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>20698</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>245966</t>
+          <t>247530</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>303279</t>
+          <t>302040</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>200533</t>
+          <t>199885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>235933</t>
+          <t>236171</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>460501</t>
+          <t>457873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>526878</t>
+          <t>528219</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,55%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112578</t>
+          <t>113168</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>164614</t>
+          <t>162987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101036</t>
+          <t>100577</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>131735</t>
+          <t>132138</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>223867</t>
+          <t>222817</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>280568</t>
+          <t>283606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43588</t>
+          <t>43261</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>77962</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28609</t>
+          <t>28147</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48623</t>
+          <t>48584</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>77585</t>
+          <t>76085</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>118171</t>
+          <t>116376</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>41114</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75706</t>
+          <t>74995</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>43684</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71933</t>
+          <t>71914</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>110583</t>
+          <t>110795</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20813</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45436</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28370</t>
+          <t>27424</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37378</t>
+          <t>37864</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65960</t>
+          <t>66700</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>125158</t>
+          <t>125136</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>159957</t>
+          <t>161671</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>186353</t>
+          <t>187737</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>294873</t>
+          <t>303128</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>333579</t>
+          <t>335041</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>457701</t>
+          <t>454106</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,11%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>40689</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>67995</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>38283</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>98104</t>
+          <t>96477</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>82463</t>
+          <t>80893</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>152113</t>
+          <t>149624</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39840</t>
+          <t>39652</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29076</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>63259</t>
+          <t>61825</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11261</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>33918</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>30767</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>24043</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>55022</t>
+          <t>56256</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>35013</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4695,107 +4695,107 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>911</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1208138</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1081546</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1451924</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>833344</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>773651</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>921677</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2041482</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1895055</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2327144</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -4808,107 +4808,107 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>378697</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>252678</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449558</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>542</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>336840</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284706</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>374992</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>947</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>715537</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>567313</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>805379</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -4921,107 +4921,107 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142323</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95785</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180239</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105707</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84572</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126684</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248030</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196140</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>289091</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -5034,107 +5034,107 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123297</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82015</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158285</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87922</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71941</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105455</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>211219</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167822</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248956</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -5147,107 +5147,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63084</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39531</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85286</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50943</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66056</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114027</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87464</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139083</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5260,107 +5260,107 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30278</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18455</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46023</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16749</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55904</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78661</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -5373,919 +5373,123 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1945817</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1945817</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1945817</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1440382</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1440382</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1440382</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3386199</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3386199</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3386199</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Nunca/ casi nunca</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>1208138</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>1086602</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1468550</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>62,09%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>55,84%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>75,47%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>1056</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>833344</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>778876</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>931343</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>54,07%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>64,66%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>2041482</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>1900132</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>2360024</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>60,29%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>56,11%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>69,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Con menos frecuencia /raramente</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>378697</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>254952</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>447212</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>22,98%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>336840</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>281447</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>372552</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>19,54%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>715537</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>558884</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>797271</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Varias veces al año</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>142323</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>96296</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>179570</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>105707</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>87011</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>126206</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>248030</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>193904</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>289811</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Varias veces al mes</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>123297</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>84459</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>156526</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>87922</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>70958</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>104402</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>211219</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>164537</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>248635</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Varias veces a la semana</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>63084</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>40149</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>84054</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>50943</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>38751</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>65576</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>114027</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>86428</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>142281</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>A diario</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>30278</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>17683</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>44619</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>25626</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>16111</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>46299</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>55904</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>41283</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>78692</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>1945817</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>1945817</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1945817</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>1440382</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>1440382</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>1440382</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>3647</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>3386199</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>3386199</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>3386199</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>

--- a/data/trans_orig/P70C3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>218880</t>
+          <t>235526</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197359</t>
+          <t>214225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236603</t>
+          <t>256461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>193711</t>
+          <t>205124</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>180128</t>
+          <t>189583</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>209235</t>
+          <t>220601</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>412591</t>
+          <t>440650</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>389605</t>
+          <t>414885</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>437772</t>
+          <t>467571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72216</t>
+          <t>81207</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56885</t>
+          <t>63929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89972</t>
+          <t>100150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68727</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56760</t>
+          <t>60857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80415</t>
+          <t>87191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>140943</t>
+          <t>154686</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121640</t>
+          <t>133483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160664</t>
+          <t>176302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34311</t>
+          <t>36930</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48859</t>
+          <t>53317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>15069</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28005</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>54191</t>
+          <t>58595</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40014</t>
+          <t>44358</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70591</t>
+          <t>75129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>20708</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21684</t>
+          <t>24265</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30482</t>
+          <t>34418</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>35367</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>24924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44795</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>16492</t>
+          <t>18993</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>12158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>29799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>19751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,22 +1325,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21195</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>316779</t>
+          <t>338251</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>316779</t>
+          <t>338251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>316779</t>
+          <t>338251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>668691</t>
+          <t>721064</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>668691</t>
+          <t>721064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>668691</t>
+          <t>721064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>184121</t>
+          <t>192710</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163820</t>
+          <t>172178</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200095</t>
+          <t>210013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146422</t>
+          <t>159042</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133033</t>
+          <t>144107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161188</t>
+          <t>172236</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>330544</t>
+          <t>351752</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307533</t>
+          <t>328259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>354228</t>
+          <t>376402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70814</t>
+          <t>75784</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>59599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87215</t>
+          <t>92106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62331</t>
+          <t>68229</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50714</t>
+          <t>57122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75501</t>
+          <t>81519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133145</t>
+          <t>144013</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115341</t>
+          <t>125815</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>153839</t>
+          <t>165951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28473</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37964</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>30822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50211</t>
+          <t>56040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>19717</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>31128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>27382</t>
+          <t>29130</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>19633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41815</t>
+          <t>41809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>25598</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>303191</t>
+          <t>320548</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>303191</t>
+          <t>320548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>303191</t>
+          <t>320548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>252166</t>
+          <t>273404</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>252166</t>
+          <t>273404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>252166</t>
+          <t>273404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>555358</t>
+          <t>593951</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>555358</t>
+          <t>593951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>555358</t>
+          <t>593951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>384396</t>
+          <t>154918</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>266202</t>
+          <t>138176</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>460067</t>
+          <t>173682</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39709</t>
+          <t>45266</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32622</t>
+          <t>37602</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46810</t>
+          <t>53959</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>424105</t>
+          <t>200184</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>309364</t>
+          <t>179566</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>516769</t>
+          <t>219851</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48510</t>
+          <t>57764</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>44046</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106235</t>
+          <t>71865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>21885</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>29311</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>68378</t>
+          <t>79649</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>64948</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127685</t>
+          <t>95902</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>23020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>26520</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44201</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47655</t>
+          <t>37880</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38771</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>17482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>37973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>20877</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>483</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>562899</t>
+          <t>355383</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>562899</t>
+          <t>355383</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>562899</t>
+          <t>355383</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,27 +3110,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>276005</t>
+          <t>306816</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>247530</t>
+          <t>279247</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>302040</t>
+          <t>334908</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>217178</t>
+          <t>246026</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>199885</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>236171</t>
+          <t>266888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>493183</t>
+          <t>552842</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>457873</t>
+          <t>519784</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>528219</t>
+          <t>587105</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>135277</t>
+          <t>149669</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113168</t>
+          <t>129224</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>162987</t>
+          <t>175510</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>115823</t>
+          <t>131583</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100577</t>
+          <t>114636</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>132138</t>
+          <t>151500</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>251100</t>
+          <t>281253</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222817</t>
+          <t>252581</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>283606</t>
+          <t>313374</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>57869</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43261</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>75048</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>37365</t>
+          <t>40461</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28147</t>
+          <t>32058</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48584</t>
+          <t>52289</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>95234</t>
+          <t>107457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>76085</t>
+          <t>89638</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>116376</t>
+          <t>132739</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>57921</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41114</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>74995</t>
+          <t>76033</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24759</t>
+          <t>25206</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43684</t>
+          <t>44720</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>89324</t>
+          <t>91922</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71914</t>
+          <t>74620</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>110795</t>
+          <t>112190</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>31287</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>47340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18287</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27424</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>49575</t>
+          <t>54935</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37864</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>66700</t>
+          <t>74510</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>560948</t>
+          <t>622033</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>560948</t>
+          <t>622033</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>560948</t>
+          <t>622033</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425537</t>
+          <t>478146</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425537</t>
+          <t>478146</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425537</t>
+          <t>478146</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>986485</t>
+          <t>1100179</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>986485</t>
+          <t>1100179</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>986485</t>
+          <t>1100179</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>144734</t>
+          <t>190948</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>125136</t>
+          <t>168477</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>161671</t>
+          <t>208910</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>236324</t>
+          <t>159080</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>187737</t>
+          <t>144576</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>303128</t>
+          <t>175910</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>381058</t>
+          <t>350028</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>335041</t>
+          <t>321460</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>454106</t>
+          <t>374008</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>60,16%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>51880</t>
+          <t>69207</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>54276</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>67995</t>
+          <t>88023</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>70091</t>
+          <t>79956</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>38083</t>
+          <t>67161</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>96477</t>
+          <t>93801</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>121971</t>
+          <t>149162</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>80893</t>
+          <t>130821</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>149624</t>
+          <t>172196</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>33811</t>
+          <t>35502</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>27116</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39652</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>45196</t>
+          <t>52629</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29125</t>
+          <t>40154</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>61825</t>
+          <t>68117</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>36858</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>19671</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>33922</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>44875</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>56256</t>
+          <t>61442</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>35957</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>35013</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>240077</t>
+          <t>308914</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>240077</t>
+          <t>308914</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>240077</t>
+          <t>308914</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>372689</t>
+          <t>312735</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>372689</t>
+          <t>312735</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>372689</t>
+          <t>312735</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>612766</t>
+          <t>621649</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>612766</t>
+          <t>621649</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>612766</t>
+          <t>621649</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1208138</t>
+          <t>1080919</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1081546</t>
+          <t>1029532</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1451924</t>
+          <t>1127843</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>833344</t>
+          <t>814537</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>773651</t>
+          <t>780339</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>921677</t>
+          <t>847466</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2041482</t>
+          <t>1895456</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1895055</t>
+          <t>1839059</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2327144</t>
+          <t>1957831</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>378697</t>
+          <t>433631</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>252678</t>
+          <t>393374</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>449558</t>
+          <t>472123</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>336840</t>
+          <t>375131</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>284706</t>
+          <t>347034</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>374992</t>
+          <t>404024</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>715537</t>
+          <t>808762</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>567313</t>
+          <t>754789</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>805379</t>
+          <t>855361</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -4926,69 +4926,69 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>142323</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>95785</t>
+          <t>132977</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>180239</t>
+          <t>190663</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>117444</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>99565</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>137530</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>105707</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>84572</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>126684</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>292</t>
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>248030</t>
+          <t>276728</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>196140</t>
+          <t>247426</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>289091</t>
+          <t>314491</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>123297</t>
+          <t>129543</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>82015</t>
+          <t>104451</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>158285</t>
+          <t>155505</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>87922</t>
+          <t>96593</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>71941</t>
+          <t>80284</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>105455</t>
+          <t>112741</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>211219</t>
+          <t>226136</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>167822</t>
+          <t>196723</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>248956</t>
+          <t>257396</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>50048</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>85286</t>
+          <t>89656</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,67 +5187,67 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>50943</t>
+          <t>59568</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>38465</t>
+          <t>46620</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>66056</t>
+          <t>75488</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>127099</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>106241</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>155626</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
           <t>4,59%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>114027</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>87464</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>139083</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>46023</t>
+          <t>50368</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>22233</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>46650</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>55904</t>
+          <t>58046</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>44799</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>78661</t>
+          <t>74844</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1945817</t>
+          <t>1906721</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1945817</t>
+          <t>1906721</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1945817</t>
+          <t>1906721</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1440382</t>
+          <t>1485506</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1440382</t>
+          <t>1485506</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1440382</t>
+          <t>1485506</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>3386199</t>
+          <t>3392227</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3386199</t>
+          <t>3392227</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3386199</t>
+          <t>3392227</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
